--- a/outputs/28-7.xlsx
+++ b/outputs/28-7.xlsx
@@ -116,12 +116,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,165 +321,165 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/28-7.xlsx
+++ b/outputs/28-7.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="5">
   <si>
     <t xml:space="preserve">400-12345-W</t>
   </si>
@@ -29,12 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">A-235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400-12345-D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X-5556</t>
   </si>
   <si>
     <t xml:space="preserve">400-12345-F</t>
@@ -395,9 +389,6 @@
       <c r="I8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -405,9 +396,6 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -415,9 +403,6 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -425,15 +410,6 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -441,9 +417,6 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -451,9 +424,6 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
